--- a/artfynd/A 30589-2025 artfynd.xlsx
+++ b/artfynd/A 30589-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134270019</v>
+        <v>134271409</v>
       </c>
       <c r="B2" t="n">
-        <v>80475</v>
+        <v>5201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523174</v>
+        <v>523339</v>
       </c>
       <c r="R2" t="n">
-        <v>6847987</v>
+        <v>6847893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134271409</v>
+        <v>134270952</v>
       </c>
       <c r="B3" t="n">
-        <v>5201</v>
+        <v>80474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523339</v>
+        <v>523244</v>
       </c>
       <c r="R3" t="n">
-        <v>6847893</v>
+        <v>6847898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134270952</v>
+        <v>134270019</v>
       </c>
       <c r="B4" t="n">
-        <v>80474</v>
+        <v>80475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523244</v>
+        <v>523174</v>
       </c>
       <c r="R4" t="n">
-        <v>6847898</v>
+        <v>6847987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1072,32 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134270911</v>
+        <v>134270669</v>
       </c>
       <c r="B6" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523255</v>
+        <v>523242</v>
       </c>
       <c r="R6" t="n">
-        <v>6847886</v>
+        <v>6847974</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,11 +1143,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100-tals plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,32 +1169,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134270669</v>
+        <v>134270911</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>99181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523242</v>
+        <v>523255</v>
       </c>
       <c r="R7" t="n">
-        <v>6847974</v>
+        <v>6847886</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,6 +1240,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>100-tals plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134271174</v>
+        <v>134271026</v>
       </c>
       <c r="B8" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523296</v>
+        <v>523262</v>
       </c>
       <c r="R8" t="n">
-        <v>6847910</v>
+        <v>6847870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134271026</v>
+        <v>134271174</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1379,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523262</v>
+        <v>523296</v>
       </c>
       <c r="R9" t="n">
-        <v>6847870</v>
+        <v>6847910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,32 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134270518</v>
+        <v>134271345</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>99203</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523216</v>
+        <v>523353</v>
       </c>
       <c r="R10" t="n">
-        <v>6848006</v>
+        <v>6847889</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134271345</v>
+        <v>134270518</v>
       </c>
       <c r="B11" t="n">
-        <v>99203</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523353</v>
+        <v>523216</v>
       </c>
       <c r="R11" t="n">
-        <v>6847889</v>
+        <v>6848006</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134271302</v>
+        <v>134270025</v>
       </c>
       <c r="B14" t="n">
-        <v>83344</v>
+        <v>80474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1864,21 +1864,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523319</v>
+        <v>523174</v>
       </c>
       <c r="R14" t="n">
-        <v>6847932</v>
+        <v>6847988</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134270025</v>
+        <v>134271302</v>
       </c>
       <c r="B15" t="n">
-        <v>80474</v>
+        <v>83344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1961,21 +1961,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523174</v>
+        <v>523319</v>
       </c>
       <c r="R15" t="n">
-        <v>6847988</v>
+        <v>6847932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2338,32 +2338,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134269892</v>
+        <v>134270413</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>79025</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523150</v>
+        <v>523200</v>
       </c>
       <c r="R19" t="n">
-        <v>6848138</v>
+        <v>6848005</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,32 +2435,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134270413</v>
+        <v>134269892</v>
       </c>
       <c r="B20" t="n">
-        <v>79025</v>
+        <v>99181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523200</v>
+        <v>523150</v>
       </c>
       <c r="R20" t="n">
-        <v>6848005</v>
+        <v>6848138</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,32 +2532,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134271156</v>
+        <v>134271244</v>
       </c>
       <c r="B21" t="n">
-        <v>99203</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523295</v>
+        <v>523303</v>
       </c>
       <c r="R21" t="n">
-        <v>6847909</v>
+        <v>6847925</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134271244</v>
+        <v>134271156</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>99203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523303</v>
+        <v>523295</v>
       </c>
       <c r="R22" t="n">
-        <v>6847925</v>
+        <v>6847909</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134283801</v>
+        <v>134284055</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523140</v>
+        <v>522854</v>
       </c>
       <c r="R24" t="n">
-        <v>6848077</v>
+        <v>6848343</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2908,22 +2908,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134283898</v>
+        <v>134283801</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523142</v>
+        <v>523140</v>
       </c>
       <c r="R25" t="n">
-        <v>6848087</v>
+        <v>6848077</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134284055</v>
+        <v>134283898</v>
       </c>
       <c r="B28" t="n">
-        <v>79391</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3231,21 +3231,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522854</v>
+        <v>523142</v>
       </c>
       <c r="R28" t="n">
-        <v>6848343</v>
+        <v>6848087</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3305,22 +3305,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134283514</v>
+        <v>134285959</v>
       </c>
       <c r="B29" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3328,21 +3328,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522980</v>
+        <v>522854</v>
       </c>
       <c r="R29" t="n">
-        <v>6848305</v>
+        <v>6848235</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3414,57 +3414,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134283717</v>
+        <v>134283595</v>
       </c>
       <c r="B30" t="n">
-        <v>99203</v>
+        <v>79391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522914</v>
+        <v>522916</v>
       </c>
       <c r="R30" t="n">
-        <v>6848340</v>
+        <v>6848309</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3508,57 +3499,66 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134285959</v>
+        <v>134283717</v>
       </c>
       <c r="B31" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522854</v>
+        <v>522914</v>
       </c>
       <c r="R31" t="n">
-        <v>6848235</v>
+        <v>6848340</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3617,45 +3617,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134283595</v>
+        <v>134283945</v>
       </c>
       <c r="B32" t="n">
-        <v>79391</v>
+        <v>99216</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522916</v>
+        <v>522878</v>
       </c>
       <c r="R32" t="n">
-        <v>6848309</v>
+        <v>6848373</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3714,62 +3728,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134283945</v>
+        <v>134283514</v>
       </c>
       <c r="B33" t="n">
-        <v>99216</v>
+        <v>79978</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219874</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522878</v>
+        <v>522980</v>
       </c>
       <c r="R33" t="n">
-        <v>6848373</v>
+        <v>6848305</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3813,12 +3813,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134284143</v>
+        <v>134285793</v>
       </c>
       <c r="B36" t="n">
-        <v>99203</v>
+        <v>79359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522849</v>
+        <v>522908</v>
       </c>
       <c r="R36" t="n">
-        <v>6848367</v>
+        <v>6848224</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134284573</v>
+        <v>134284143</v>
       </c>
       <c r="B37" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523213</v>
+        <v>522849</v>
       </c>
       <c r="R37" t="n">
-        <v>6848024</v>
+        <v>6848367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4201,19 +4201,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134285793</v>
+        <v>134284573</v>
       </c>
       <c r="B38" t="n">
         <v>79359</v>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522908</v>
+        <v>523213</v>
       </c>
       <c r="R38" t="n">
-        <v>6848224</v>
+        <v>6848024</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4298,22 +4298,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134282795</v>
+        <v>134282904</v>
       </c>
       <c r="B39" t="n">
-        <v>99085</v>
+        <v>99098</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4321,21 +4321,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523156</v>
+        <v>523134</v>
       </c>
       <c r="R39" t="n">
-        <v>6848154</v>
+        <v>6848161</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4407,10 +4407,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134282904</v>
+        <v>134282795</v>
       </c>
       <c r="B40" t="n">
-        <v>99098</v>
+        <v>99085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4418,21 +4418,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523134</v>
+        <v>523156</v>
       </c>
       <c r="R40" t="n">
-        <v>6848161</v>
+        <v>6848154</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4814,57 +4814,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134284010</v>
+        <v>134284836</v>
       </c>
       <c r="B44" t="n">
-        <v>99216</v>
+        <v>79359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522849</v>
+        <v>523054</v>
       </c>
       <c r="R44" t="n">
-        <v>6848367</v>
+        <v>6848168</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4908,12 +4899,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5017,45 +5008,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134283503</v>
+        <v>134284010</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>99216</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523084</v>
+        <v>522849</v>
       </c>
       <c r="R46" t="n">
-        <v>6848078</v>
+        <v>6848367</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5102,22 +5102,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134284836</v>
+        <v>134283503</v>
       </c>
       <c r="B47" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5125,21 +5125,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5149,13 +5149,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523054</v>
+        <v>523084</v>
       </c>
       <c r="R47" t="n">
-        <v>6848168</v>
+        <v>6848078</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5199,12 +5199,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134291270</v>
+        <v>134284462</v>
       </c>
       <c r="B49" t="n">
-        <v>91980</v>
+        <v>79359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5328,33 +5328,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slåttkölen, Hls</t>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523113</v>
+        <v>522861</v>
       </c>
       <c r="R49" t="n">
-        <v>6848141</v>
+        <v>6848290</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,29 +5396,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134284462</v>
+        <v>134291270</v>
       </c>
       <c r="B50" t="n">
-        <v>79359</v>
+        <v>91980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5425,34 +5425,33 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slåttkölen, Slåttkölen, Hls</t>
+          <t>Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522861</v>
+        <v>523113</v>
       </c>
       <c r="R50" t="n">
-        <v>6848290</v>
+        <v>6848141</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5493,18 +5492,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134284059</v>
+        <v>134285146</v>
       </c>
       <c r="B54" t="n">
         <v>99181</v>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522849</v>
+        <v>523055</v>
       </c>
       <c r="R54" t="n">
-        <v>6848367</v>
+        <v>6848075</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5926,7 +5926,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134285146</v>
+        <v>134284059</v>
       </c>
       <c r="B55" t="n">
         <v>99181</v>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523055</v>
+        <v>522849</v>
       </c>
       <c r="R55" t="n">
-        <v>6848075</v>
+        <v>6848367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134283528</v>
+        <v>134286052</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6334,21 +6334,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522968</v>
+        <v>522811</v>
       </c>
       <c r="R59" t="n">
-        <v>6848309</v>
+        <v>6848265</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6420,10 +6420,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134286052</v>
+        <v>134283528</v>
       </c>
       <c r="B60" t="n">
-        <v>79117</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,21 +6431,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,13 +6455,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522811</v>
+        <v>522968</v>
       </c>
       <c r="R60" t="n">
-        <v>6848265</v>
+        <v>6848309</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6517,32 +6517,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134284003</v>
+        <v>134283986</v>
       </c>
       <c r="B61" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523115</v>
+        <v>523116</v>
       </c>
       <c r="R61" t="n">
         <v>6848146</v>
@@ -6711,32 +6711,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134283986</v>
+        <v>134284003</v>
       </c>
       <c r="B63" t="n">
-        <v>99203</v>
+        <v>79359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523116</v>
+        <v>523115</v>
       </c>
       <c r="R63" t="n">
         <v>6848146</v>
@@ -6910,7 +6910,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134282799</v>
+        <v>134285939</v>
       </c>
       <c r="B65" t="n">
         <v>79116</v>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523098</v>
+        <v>522853</v>
       </c>
       <c r="R65" t="n">
-        <v>6848178</v>
+        <v>6848230</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134285939</v>
+        <v>134282799</v>
       </c>
       <c r="B66" t="n">
         <v>79116</v>
@@ -7042,10 +7042,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522853</v>
+        <v>523098</v>
       </c>
       <c r="R66" t="n">
-        <v>6848230</v>
+        <v>6848178</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7104,32 +7104,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134283788</v>
+        <v>134284567</v>
       </c>
       <c r="B67" t="n">
-        <v>99203</v>
+        <v>92013</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7139,13 +7139,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522911</v>
+        <v>523213</v>
       </c>
       <c r="R67" t="n">
-        <v>6848359</v>
+        <v>6848025</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7189,44 +7189,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134283461</v>
+        <v>134283788</v>
       </c>
       <c r="B68" t="n">
-        <v>79116</v>
+        <v>99203</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7236,13 +7236,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523077</v>
+        <v>522911</v>
       </c>
       <c r="R68" t="n">
-        <v>6848084</v>
+        <v>6848359</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7286,22 +7286,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134284567</v>
+        <v>134283461</v>
       </c>
       <c r="B69" t="n">
-        <v>92013</v>
+        <v>79116</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7309,21 +7309,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7333,10 +7333,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523213</v>
+        <v>523077</v>
       </c>
       <c r="R69" t="n">
-        <v>6848025</v>
+        <v>6848084</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7501,32 +7501,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134283046</v>
+        <v>134282982</v>
       </c>
       <c r="B71" t="n">
-        <v>79117</v>
+        <v>56925</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>208260</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523038</v>
+        <v>523056</v>
       </c>
       <c r="R71" t="n">
-        <v>6848219</v>
+        <v>6848227</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7695,32 +7695,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134282982</v>
+        <v>134283046</v>
       </c>
       <c r="B73" t="n">
-        <v>56925</v>
+        <v>79117</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>208260</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523056</v>
+        <v>523038</v>
       </c>
       <c r="R73" t="n">
-        <v>6848227</v>
+        <v>6848219</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7792,32 +7792,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134283939</v>
+        <v>134283974</v>
       </c>
       <c r="B74" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523131</v>
+        <v>523115</v>
       </c>
       <c r="R74" t="n">
-        <v>6848127</v>
+        <v>6848146</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7889,32 +7889,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134283632</v>
+        <v>134283973</v>
       </c>
       <c r="B75" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,13 +7924,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523131</v>
+        <v>522850</v>
       </c>
       <c r="R75" t="n">
-        <v>6848022</v>
+        <v>6848362</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7974,19 +7974,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134283380</v>
+        <v>134283939</v>
       </c>
       <c r="B76" t="n">
         <v>79359</v>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523047</v>
+        <v>523131</v>
       </c>
       <c r="R76" t="n">
-        <v>6848103</v>
+        <v>6848127</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8083,32 +8083,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134283974</v>
+        <v>134283632</v>
       </c>
       <c r="B77" t="n">
-        <v>99203</v>
+        <v>79359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523115</v>
+        <v>523131</v>
       </c>
       <c r="R77" t="n">
-        <v>6848146</v>
+        <v>6848022</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8180,32 +8180,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134283973</v>
+        <v>134283380</v>
       </c>
       <c r="B78" t="n">
-        <v>99203</v>
+        <v>79359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8215,13 +8215,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522850</v>
+        <v>523047</v>
       </c>
       <c r="R78" t="n">
-        <v>6848362</v>
+        <v>6848103</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8265,12 +8265,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 30589-2025 artfynd.xlsx
+++ b/artfynd/A 30589-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134271409</v>
+        <v>134270952</v>
       </c>
       <c r="B2" t="n">
-        <v>5201</v>
+        <v>80481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523339</v>
+        <v>523244</v>
       </c>
       <c r="R2" t="n">
-        <v>6847893</v>
+        <v>6847898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134270952</v>
+        <v>134270019</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>80482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523244</v>
+        <v>523174</v>
       </c>
       <c r="R3" t="n">
-        <v>6847898</v>
+        <v>6847987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134270019</v>
+        <v>134271409</v>
       </c>
       <c r="B4" t="n">
-        <v>80475</v>
+        <v>5201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523174</v>
+        <v>523339</v>
       </c>
       <c r="R4" t="n">
-        <v>6847987</v>
+        <v>6847893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>134269855</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>134270669</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>134270911</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134271026</v>
+        <v>134271174</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>80481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523262</v>
+        <v>523296</v>
       </c>
       <c r="R8" t="n">
-        <v>6847870</v>
+        <v>6847910</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134271174</v>
+        <v>134271026</v>
       </c>
       <c r="B9" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1379,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523296</v>
+        <v>523262</v>
       </c>
       <c r="R9" t="n">
-        <v>6847910</v>
+        <v>6847870</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>134271345</v>
       </c>
       <c r="B10" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>134270518</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>134271337</v>
       </c>
       <c r="B12" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>134271257</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134270025</v>
+        <v>134271302</v>
       </c>
       <c r="B14" t="n">
-        <v>80474</v>
+        <v>83351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1864,21 +1864,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523174</v>
+        <v>523319</v>
       </c>
       <c r="R14" t="n">
-        <v>6847988</v>
+        <v>6847932</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134271302</v>
+        <v>134270025</v>
       </c>
       <c r="B15" t="n">
-        <v>83344</v>
+        <v>80481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1961,21 +1961,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523319</v>
+        <v>523174</v>
       </c>
       <c r="R15" t="n">
-        <v>6847932</v>
+        <v>6847988</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134270921</v>
+        <v>134270739</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523257</v>
+        <v>523236</v>
       </c>
       <c r="R16" t="n">
-        <v>6847883</v>
+        <v>6847958</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134270739</v>
+        <v>134270921</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523236</v>
+        <v>523257</v>
       </c>
       <c r="R17" t="n">
-        <v>6847958</v>
+        <v>6847883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2244,7 +2244,7 @@
         <v>134271170</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,32 +2338,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134270413</v>
+        <v>134269892</v>
       </c>
       <c r="B19" t="n">
-        <v>79025</v>
+        <v>99188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523200</v>
+        <v>523150</v>
       </c>
       <c r="R19" t="n">
-        <v>6848005</v>
+        <v>6848138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,32 +2435,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134269892</v>
+        <v>134270413</v>
       </c>
       <c r="B20" t="n">
-        <v>99181</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523150</v>
+        <v>523200</v>
       </c>
       <c r="R20" t="n">
-        <v>6848138</v>
+        <v>6848005</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2532,32 +2532,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134271244</v>
+        <v>134271156</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>99210</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523303</v>
+        <v>523295</v>
       </c>
       <c r="R21" t="n">
-        <v>6847925</v>
+        <v>6847909</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134271156</v>
+        <v>134271244</v>
       </c>
       <c r="B22" t="n">
-        <v>99203</v>
+        <v>79123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523295</v>
+        <v>523303</v>
       </c>
       <c r="R22" t="n">
-        <v>6847909</v>
+        <v>6847925</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>134269878</v>
       </c>
       <c r="B23" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134284055</v>
+        <v>134283801</v>
       </c>
       <c r="B24" t="n">
-        <v>79391</v>
+        <v>79123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522854</v>
+        <v>523140</v>
       </c>
       <c r="R24" t="n">
-        <v>6848343</v>
+        <v>6848077</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2908,22 +2908,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134283801</v>
+        <v>134283898</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523140</v>
+        <v>523142</v>
       </c>
       <c r="R25" t="n">
-        <v>6848077</v>
+        <v>6848087</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>134283743</v>
       </c>
       <c r="B26" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,54 +3114,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134283359</v>
+        <v>134284055</v>
       </c>
       <c r="B27" t="n">
-        <v>99203</v>
+        <v>79398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522992</v>
+        <v>522854</v>
       </c>
       <c r="R27" t="n">
-        <v>6848297</v>
+        <v>6848343</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3220,48 +3211,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134283898</v>
+        <v>134283359</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>99210</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523142</v>
+        <v>522992</v>
       </c>
       <c r="R28" t="n">
-        <v>6848087</v>
+        <v>6848297</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3305,22 +3305,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134285959</v>
+        <v>134283514</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3328,21 +3328,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522854</v>
+        <v>522980</v>
       </c>
       <c r="R29" t="n">
-        <v>6848235</v>
+        <v>6848305</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3414,48 +3414,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134283595</v>
+        <v>134283717</v>
       </c>
       <c r="B30" t="n">
-        <v>79391</v>
+        <v>99210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522916</v>
+        <v>522914</v>
       </c>
       <c r="R30" t="n">
-        <v>6848309</v>
+        <v>6848340</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3499,66 +3508,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134283717</v>
+        <v>134285959</v>
       </c>
       <c r="B31" t="n">
-        <v>99203</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522914</v>
+        <v>522854</v>
       </c>
       <c r="R31" t="n">
-        <v>6848340</v>
+        <v>6848235</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
         <v>134283945</v>
       </c>
       <c r="B32" t="n">
-        <v>99216</v>
+        <v>99223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134283514</v>
+        <v>134283595</v>
       </c>
       <c r="B33" t="n">
-        <v>79978</v>
+        <v>79398</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3739,21 +3739,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3763,13 +3763,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522980</v>
+        <v>522916</v>
       </c>
       <c r="R33" t="n">
-        <v>6848305</v>
+        <v>6848309</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3813,12 +3813,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3828,7 +3828,7 @@
         <v>134282793</v>
       </c>
       <c r="B34" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>134283961</v>
       </c>
       <c r="B35" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4019,32 +4019,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134285793</v>
+        <v>134284143</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>99210</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522908</v>
+        <v>522849</v>
       </c>
       <c r="R36" t="n">
-        <v>6848224</v>
+        <v>6848367</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4116,32 +4116,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134284143</v>
+        <v>134285793</v>
       </c>
       <c r="B37" t="n">
-        <v>99203</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522849</v>
+        <v>522908</v>
       </c>
       <c r="R37" t="n">
-        <v>6848367</v>
+        <v>6848224</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4216,7 +4216,7 @@
         <v>134284573</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134282904</v>
+        <v>134286811</v>
       </c>
       <c r="B39" t="n">
-        <v>99098</v>
+        <v>57162</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4321,21 +4321,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523134</v>
+        <v>523168</v>
       </c>
       <c r="R39" t="n">
-        <v>6848161</v>
+        <v>6848179</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4381,6 +4381,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4410,7 +4415,7 @@
         <v>134282795</v>
       </c>
       <c r="B40" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4504,10 +4509,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134286811</v>
+        <v>134282904</v>
       </c>
       <c r="B41" t="n">
-        <v>57162</v>
+        <v>99105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4515,21 +4520,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4539,10 +4544,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523168</v>
+        <v>523134</v>
       </c>
       <c r="R41" t="n">
-        <v>6848179</v>
+        <v>6848161</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,11 +4580,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4609,7 +4609,7 @@
         <v>134283829</v>
       </c>
       <c r="B42" t="n">
-        <v>99216</v>
+        <v>99223</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>134285967</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>134284836</v>
       </c>
       <c r="B44" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4911,45 +4911,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134283024</v>
+        <v>134284010</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>99223</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523056</v>
+        <v>522849</v>
       </c>
       <c r="R45" t="n">
-        <v>6848228</v>
+        <v>6848367</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5008,54 +5017,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134284010</v>
+        <v>134283024</v>
       </c>
       <c r="B46" t="n">
-        <v>99216</v>
+        <v>79123</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522849</v>
+        <v>523056</v>
       </c>
       <c r="R46" t="n">
-        <v>6848367</v>
+        <v>6848228</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
         <v>134283503</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,54 +5211,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134283544</v>
+        <v>134284462</v>
       </c>
       <c r="B48" t="n">
-        <v>99181</v>
+        <v>79366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522963</v>
+        <v>522861</v>
       </c>
       <c r="R48" t="n">
-        <v>6848312</v>
+        <v>6848290</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5305,22 +5296,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134284462</v>
+        <v>134291270</v>
       </c>
       <c r="B49" t="n">
-        <v>79359</v>
+        <v>91987</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5328,34 +5319,33 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slåttkölen, Slåttkölen, Hls</t>
+          <t>Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522861</v>
+        <v>523113</v>
       </c>
       <c r="R49" t="n">
-        <v>6848290</v>
+        <v>6848141</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5396,62 +5386,73 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134291270</v>
+        <v>134283544</v>
       </c>
       <c r="B50" t="n">
-        <v>91980</v>
+        <v>99188</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slåttkölen, Hls</t>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523113</v>
+        <v>522963</v>
       </c>
       <c r="R50" t="n">
-        <v>6848141</v>
+        <v>6848312</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,29 +5493,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134286773</v>
+        <v>134284129</v>
       </c>
       <c r="B51" t="n">
-        <v>99085</v>
+        <v>98059</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5522,21 +5522,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220093</v>
+        <v>221941</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523142</v>
+        <v>522848</v>
       </c>
       <c r="R51" t="n">
-        <v>6848167</v>
+        <v>6848342</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5605,22 +5605,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134284129</v>
+        <v>134286773</v>
       </c>
       <c r="B52" t="n">
-        <v>98052</v>
+        <v>99092</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5628,21 +5628,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>220093</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5661,13 +5661,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522848</v>
+        <v>523142</v>
       </c>
       <c r="R52" t="n">
-        <v>6848342</v>
+        <v>6848167</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5711,12 +5711,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5726,7 +5726,7 @@
         <v>134284856</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134285146</v>
+        <v>134284059</v>
       </c>
       <c r="B54" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523055</v>
+        <v>522849</v>
       </c>
       <c r="R54" t="n">
-        <v>6848075</v>
+        <v>6848367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134284059</v>
+        <v>134285146</v>
       </c>
       <c r="B55" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522849</v>
+        <v>523055</v>
       </c>
       <c r="R55" t="n">
-        <v>6848367</v>
+        <v>6848075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134283275</v>
+        <v>134283528</v>
       </c>
       <c r="B56" t="n">
-        <v>97421</v>
+        <v>79123</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523047</v>
+        <v>522968</v>
       </c>
       <c r="R56" t="n">
-        <v>6848112</v>
+        <v>6848309</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6117,22 +6117,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134285322</v>
+        <v>134283275</v>
       </c>
       <c r="B57" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523200</v>
+        <v>523047</v>
       </c>
       <c r="R57" t="n">
-        <v>6847770</v>
+        <v>6848112</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6226,32 +6226,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134283888</v>
+        <v>134286052</v>
       </c>
       <c r="B58" t="n">
-        <v>99203</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522897</v>
+        <v>522811</v>
       </c>
       <c r="R58" t="n">
-        <v>6848375</v>
+        <v>6848265</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6323,32 +6323,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134286052</v>
+        <v>134283888</v>
       </c>
       <c r="B59" t="n">
-        <v>79117</v>
+        <v>99210</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522811</v>
+        <v>522897</v>
       </c>
       <c r="R59" t="n">
-        <v>6848265</v>
+        <v>6848375</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6420,10 +6420,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134283528</v>
+        <v>134285322</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>97428</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,21 +6431,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522968</v>
+        <v>523200</v>
       </c>
       <c r="R60" t="n">
-        <v>6848309</v>
+        <v>6847770</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6505,44 +6505,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134283986</v>
+        <v>134283498</v>
       </c>
       <c r="B61" t="n">
-        <v>99203</v>
+        <v>79398</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6552,13 +6552,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523116</v>
+        <v>522978</v>
       </c>
       <c r="R61" t="n">
-        <v>6848146</v>
+        <v>6848305</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6602,44 +6602,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134283498</v>
+        <v>134283986</v>
       </c>
       <c r="B62" t="n">
-        <v>79391</v>
+        <v>99210</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6649,13 +6649,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522978</v>
+        <v>523116</v>
       </c>
       <c r="R62" t="n">
-        <v>6848305</v>
+        <v>6848146</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6699,12 +6699,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6714,7 +6714,7 @@
         <v>134284003</v>
       </c>
       <c r="B63" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6808,32 +6808,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134282861</v>
+        <v>134285939</v>
       </c>
       <c r="B64" t="n">
-        <v>5181</v>
+        <v>79123</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6843,13 +6843,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523134</v>
+        <v>522853</v>
       </c>
       <c r="R64" t="n">
-        <v>6848170</v>
+        <v>6848230</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6879,11 +6879,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6898,44 +6893,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134285939</v>
+        <v>134282861</v>
       </c>
       <c r="B65" t="n">
-        <v>79116</v>
+        <v>5181</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6945,13 +6940,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>522853</v>
+        <v>523134</v>
       </c>
       <c r="R65" t="n">
-        <v>6848230</v>
+        <v>6848170</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6981,6 +6976,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6995,12 +6995,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7010,7 +7010,7 @@
         <v>134282799</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>134284567</v>
       </c>
       <c r="B67" t="n">
-        <v>92013</v>
+        <v>92020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7201,45 +7201,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134283788</v>
+        <v>134285196</v>
       </c>
       <c r="B68" t="n">
-        <v>99203</v>
+        <v>99188</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>522911</v>
+        <v>523046</v>
       </c>
       <c r="R68" t="n">
-        <v>6848359</v>
+        <v>6848083</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7301,7 +7310,7 @@
         <v>134283461</v>
       </c>
       <c r="B69" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7395,54 +7404,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134285196</v>
+        <v>134283788</v>
       </c>
       <c r="B70" t="n">
-        <v>99181</v>
+        <v>99210</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523046</v>
+        <v>522911</v>
       </c>
       <c r="R70" t="n">
-        <v>6848083</v>
+        <v>6848359</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7501,32 +7501,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134282982</v>
+        <v>134283046</v>
       </c>
       <c r="B71" t="n">
-        <v>56925</v>
+        <v>79124</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>208260</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523056</v>
+        <v>523038</v>
       </c>
       <c r="R71" t="n">
-        <v>6848227</v>
+        <v>6848219</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7601,7 +7601,7 @@
         <v>134282695</v>
       </c>
       <c r="B72" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7695,32 +7695,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134283046</v>
+        <v>134282982</v>
       </c>
       <c r="B73" t="n">
-        <v>79117</v>
+        <v>56925</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>208260</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523038</v>
+        <v>523056</v>
       </c>
       <c r="R73" t="n">
-        <v>6848219</v>
+        <v>6848227</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7792,10 +7792,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134283974</v>
+        <v>134283973</v>
       </c>
       <c r="B74" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523115</v>
+        <v>522850</v>
       </c>
       <c r="R74" t="n">
-        <v>6848146</v>
+        <v>6848362</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7877,44 +7877,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134283973</v>
+        <v>134283939</v>
       </c>
       <c r="B75" t="n">
-        <v>99203</v>
+        <v>79366</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,13 +7924,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522850</v>
+        <v>523131</v>
       </c>
       <c r="R75" t="n">
-        <v>6848362</v>
+        <v>6848127</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7974,22 +7974,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134283939</v>
+        <v>134283380</v>
       </c>
       <c r="B76" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523131</v>
+        <v>523047</v>
       </c>
       <c r="R76" t="n">
-        <v>6848127</v>
+        <v>6848103</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8083,32 +8083,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134283632</v>
+        <v>134283974</v>
       </c>
       <c r="B77" t="n">
-        <v>79359</v>
+        <v>99210</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523131</v>
+        <v>523115</v>
       </c>
       <c r="R77" t="n">
-        <v>6848022</v>
+        <v>6848146</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8180,10 +8180,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134283380</v>
+        <v>134283632</v>
       </c>
       <c r="B78" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523047</v>
+        <v>523131</v>
       </c>
       <c r="R78" t="n">
-        <v>6848103</v>
+        <v>6848022</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 30589-2025 artfynd.xlsx
+++ b/artfynd/A 30589-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134270952</v>
+        <v>134283498</v>
       </c>
       <c r="B2" t="n">
-        <v>80481</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523244</v>
+        <v>522978</v>
       </c>
       <c r="R2" t="n">
-        <v>6847898</v>
+        <v>6848305</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134270019</v>
+        <v>134283595</v>
       </c>
       <c r="B3" t="n">
-        <v>80482</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523174</v>
+        <v>522916</v>
       </c>
       <c r="R3" t="n">
-        <v>6847987</v>
+        <v>6848309</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134271409</v>
+        <v>134284055</v>
       </c>
       <c r="B4" t="n">
-        <v>5201</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523339</v>
+        <v>522854</v>
       </c>
       <c r="R4" t="n">
-        <v>6847893</v>
+        <v>6848343</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -959,64 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134269855</v>
+        <v>134284727</v>
       </c>
       <c r="B5" t="n">
-        <v>99188</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523144</v>
+        <v>523008</v>
       </c>
       <c r="R5" t="n">
-        <v>6848138</v>
+        <v>6848186</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1040,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1060,26 +1051,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134270669</v>
+        <v>134284462</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523242</v>
+        <v>522861</v>
       </c>
       <c r="R6" t="n">
-        <v>6847974</v>
+        <v>6848290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1137,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1157,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134270911</v>
+        <v>134285793</v>
       </c>
       <c r="B7" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523255</v>
+        <v>522908</v>
       </c>
       <c r="R7" t="n">
-        <v>6847886</v>
+        <v>6848224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1234,17 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>100-tals plantor</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134271174</v>
+        <v>134285959</v>
       </c>
       <c r="B8" t="n">
-        <v>80481</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523296</v>
+        <v>522854</v>
       </c>
       <c r="R8" t="n">
-        <v>6847910</v>
+        <v>6848235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1336,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1356,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134271026</v>
+        <v>134283528</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523262</v>
+        <v>522968</v>
       </c>
       <c r="R9" t="n">
-        <v>6847870</v>
+        <v>6848309</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1433,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1453,44 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134271345</v>
+        <v>134285939</v>
       </c>
       <c r="B10" t="n">
-        <v>99210</v>
+        <v>79130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523353</v>
+        <v>522853</v>
       </c>
       <c r="R10" t="n">
-        <v>6847889</v>
+        <v>6848230</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1530,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1550,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134270518</v>
+        <v>134285967</v>
       </c>
       <c r="B11" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523216</v>
+        <v>522854</v>
       </c>
       <c r="R11" t="n">
-        <v>6848006</v>
+        <v>6848235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1627,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1647,44 +1633,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134271337</v>
+        <v>134283514</v>
       </c>
       <c r="B12" t="n">
-        <v>99092</v>
+        <v>79992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1694,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523353</v>
+        <v>522980</v>
       </c>
       <c r="R12" t="n">
-        <v>6847888</v>
+        <v>6848305</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1724,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1744,57 +1730,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134271257</v>
+        <v>134283696</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>58131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103023</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523317</v>
+        <v>522914</v>
       </c>
       <c r="R13" t="n">
-        <v>6847925</v>
+        <v>6848339</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1821,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1841,60 +1832,74 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134271302</v>
+        <v>134283829</v>
       </c>
       <c r="B14" t="n">
-        <v>83351</v>
+        <v>99230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>219874</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523319</v>
+        <v>522908</v>
       </c>
       <c r="R14" t="n">
-        <v>6847932</v>
+        <v>6848355</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1918,12 +1923,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,60 +1943,74 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134270025</v>
+        <v>134283945</v>
       </c>
       <c r="B15" t="n">
-        <v>80481</v>
+        <v>99230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523174</v>
+        <v>522878</v>
       </c>
       <c r="R15" t="n">
-        <v>6847988</v>
+        <v>6848373</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2015,12 +2034,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2035,57 +2054,66 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134270739</v>
+        <v>134284010</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>99230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523236</v>
+        <v>522849</v>
       </c>
       <c r="R16" t="n">
-        <v>6847958</v>
+        <v>6848367</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2112,12 +2140,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2132,57 +2160,66 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134270921</v>
+        <v>134283544</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523257</v>
+        <v>522963</v>
       </c>
       <c r="R17" t="n">
-        <v>6847883</v>
+        <v>6848312</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2209,12 +2246,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2229,57 +2266,66 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134271170</v>
+        <v>134284059</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523296</v>
+        <v>522849</v>
       </c>
       <c r="R18" t="n">
-        <v>6847910</v>
+        <v>6848367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2306,12 +2352,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2326,60 +2372,69 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134269892</v>
+        <v>134284129</v>
       </c>
       <c r="B19" t="n">
-        <v>99188</v>
+        <v>98066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523150</v>
+        <v>522848</v>
       </c>
       <c r="R19" t="n">
-        <v>6848138</v>
+        <v>6848342</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2403,12 +2458,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2423,60 +2478,69 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134270413</v>
+        <v>134283359</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>99217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523200</v>
+        <v>522992</v>
       </c>
       <c r="R20" t="n">
-        <v>6848005</v>
+        <v>6848297</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2500,12 +2564,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2520,22 +2584,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134271156</v>
+        <v>134283717</v>
       </c>
       <c r="B21" t="n">
-        <v>99210</v>
+        <v>99217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2560,17 +2624,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523295</v>
+        <v>522914</v>
       </c>
       <c r="R21" t="n">
-        <v>6847909</v>
+        <v>6848340</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2597,12 +2670,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2617,44 +2690,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134271244</v>
+        <v>134283743</v>
       </c>
       <c r="B22" t="n">
-        <v>79123</v>
+        <v>99217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,13 +2737,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523303</v>
+        <v>522914</v>
       </c>
       <c r="R22" t="n">
-        <v>6847925</v>
+        <v>6848360</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2694,12 +2767,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2714,44 +2787,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134269878</v>
+        <v>134283788</v>
       </c>
       <c r="B23" t="n">
-        <v>80481</v>
+        <v>99217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,13 +2834,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523151</v>
+        <v>522911</v>
       </c>
       <c r="R23" t="n">
-        <v>6848140</v>
+        <v>6848359</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2791,12 +2864,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2811,44 +2884,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134283801</v>
+        <v>134283888</v>
       </c>
       <c r="B24" t="n">
-        <v>79123</v>
+        <v>99217</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,13 +2931,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523140</v>
+        <v>522897</v>
       </c>
       <c r="R24" t="n">
-        <v>6848077</v>
+        <v>6848375</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2908,44 +2981,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134283898</v>
+        <v>134283961</v>
       </c>
       <c r="B25" t="n">
-        <v>79366</v>
+        <v>99217</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,13 +3028,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523142</v>
+        <v>522853</v>
       </c>
       <c r="R25" t="n">
-        <v>6848087</v>
+        <v>6848377</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3005,22 +3078,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134283743</v>
+        <v>134283973</v>
       </c>
       <c r="B26" t="n">
-        <v>99210</v>
+        <v>99217</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,13 +3125,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522914</v>
+        <v>522850</v>
       </c>
       <c r="R26" t="n">
-        <v>6848360</v>
+        <v>6848362</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3114,32 +3187,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134284055</v>
+        <v>134284143</v>
       </c>
       <c r="B27" t="n">
-        <v>79398</v>
+        <v>99217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,13 +3222,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522854</v>
+        <v>522849</v>
       </c>
       <c r="R27" t="n">
-        <v>6848343</v>
+        <v>6848367</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3199,69 +3272,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134283359</v>
+        <v>134283046</v>
       </c>
       <c r="B28" t="n">
-        <v>99210</v>
+        <v>79131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522992</v>
+        <v>523038</v>
       </c>
       <c r="R28" t="n">
-        <v>6848297</v>
+        <v>6848219</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3305,22 +3369,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134283514</v>
+        <v>134286052</v>
       </c>
       <c r="B29" t="n">
-        <v>79985</v>
+        <v>79131</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3328,21 +3392,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3352,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522980</v>
+        <v>522811</v>
       </c>
       <c r="R29" t="n">
-        <v>6848305</v>
+        <v>6848265</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3414,54 +3478,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134283717</v>
+        <v>134283275</v>
       </c>
       <c r="B30" t="n">
-        <v>99210</v>
+        <v>97435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522914</v>
+        <v>523047</v>
       </c>
       <c r="R30" t="n">
-        <v>6848340</v>
+        <v>6848112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,22 +3563,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134285959</v>
+        <v>134285322</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>97435</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3531,21 +3586,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3555,10 +3610,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522854</v>
+        <v>523200</v>
       </c>
       <c r="R31" t="n">
-        <v>6848235</v>
+        <v>6847770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,74 +3660,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134283945</v>
+        <v>134270413</v>
       </c>
       <c r="B32" t="n">
-        <v>99223</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522878</v>
+        <v>523200</v>
       </c>
       <c r="R32" t="n">
-        <v>6848373</v>
+        <v>6848005</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3696,12 +3737,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3716,22 +3757,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134283595</v>
+        <v>134284567</v>
       </c>
       <c r="B33" t="n">
-        <v>79398</v>
+        <v>92027</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3739,21 +3780,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3763,13 +3804,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522916</v>
+        <v>523213</v>
       </c>
       <c r="R33" t="n">
-        <v>6848309</v>
+        <v>6848025</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3813,22 +3854,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134282793</v>
+        <v>134270019</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>80489</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3836,21 +3877,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3860,10 +3901,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523097</v>
+        <v>523174</v>
       </c>
       <c r="R34" t="n">
-        <v>6848178</v>
+        <v>6847987</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,12 +3931,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3910,44 +3951,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134283961</v>
+        <v>134270244</v>
       </c>
       <c r="B35" t="n">
-        <v>99210</v>
+        <v>80489</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,13 +3998,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522853</v>
+        <v>523172</v>
       </c>
       <c r="R35" t="n">
-        <v>6848377</v>
+        <v>6847947</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3987,12 +4028,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4007,44 +4048,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134284143</v>
+        <v>134270669</v>
       </c>
       <c r="B36" t="n">
-        <v>99210</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4054,10 +4095,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522849</v>
+        <v>523242</v>
       </c>
       <c r="R36" t="n">
-        <v>6848367</v>
+        <v>6847974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,12 +4125,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4104,26 +4145,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134285793</v>
+        <v>134270739</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4151,10 +4192,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522908</v>
+        <v>523236</v>
       </c>
       <c r="R37" t="n">
-        <v>6848224</v>
+        <v>6847958</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,12 +4222,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4201,26 +4242,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134284573</v>
+        <v>134270921</v>
       </c>
       <c r="B38" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4248,10 +4289,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523213</v>
+        <v>523257</v>
       </c>
       <c r="R38" t="n">
-        <v>6848024</v>
+        <v>6847883</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,12 +4319,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4310,32 +4351,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134286811</v>
+        <v>134271026</v>
       </c>
       <c r="B39" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4345,10 +4386,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523168</v>
+        <v>523262</v>
       </c>
       <c r="R39" t="n">
-        <v>6848179</v>
+        <v>6847870</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4375,17 +4416,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4412,32 +4448,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134282795</v>
+        <v>134271170</v>
       </c>
       <c r="B40" t="n">
-        <v>99092</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4447,10 +4483,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523156</v>
+        <v>523296</v>
       </c>
       <c r="R40" t="n">
-        <v>6848154</v>
+        <v>6847910</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4477,12 +4513,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4509,32 +4545,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134282904</v>
+        <v>134271257</v>
       </c>
       <c r="B41" t="n">
-        <v>99105</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4544,10 +4580,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523134</v>
+        <v>523317</v>
       </c>
       <c r="R41" t="n">
-        <v>6848161</v>
+        <v>6847925</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4574,12 +4610,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4606,62 +4642,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134283829</v>
+        <v>134283380</v>
       </c>
       <c r="B42" t="n">
-        <v>99223</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522908</v>
+        <v>523047</v>
       </c>
       <c r="R42" t="n">
-        <v>6848355</v>
+        <v>6848103</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4705,44 +4727,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134285967</v>
+        <v>134283632</v>
       </c>
       <c r="B43" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4752,10 +4774,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522854</v>
+        <v>523131</v>
       </c>
       <c r="R43" t="n">
-        <v>6848235</v>
+        <v>6848022</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,26 +4824,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134284836</v>
+        <v>134283898</v>
       </c>
       <c r="B44" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4849,13 +4871,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523054</v>
+        <v>523142</v>
       </c>
       <c r="R44" t="n">
-        <v>6848168</v>
+        <v>6848087</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4899,66 +4921,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134284010</v>
+        <v>134283939</v>
       </c>
       <c r="B45" t="n">
-        <v>99223</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522849</v>
+        <v>523131</v>
       </c>
       <c r="R45" t="n">
-        <v>6848367</v>
+        <v>6848127</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5005,44 +5018,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134283024</v>
+        <v>134284003</v>
       </c>
       <c r="B46" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5052,10 +5065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523056</v>
+        <v>523115</v>
       </c>
       <c r="R46" t="n">
-        <v>6848228</v>
+        <v>6848146</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5102,44 +5115,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134283503</v>
+        <v>134284573</v>
       </c>
       <c r="B47" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5149,10 +5162,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523084</v>
+        <v>523213</v>
       </c>
       <c r="R47" t="n">
-        <v>6848078</v>
+        <v>6848024</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5211,14 +5224,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134284462</v>
+        <v>134284836</v>
       </c>
       <c r="B48" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5246,13 +5259,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522861</v>
+        <v>523054</v>
       </c>
       <c r="R48" t="n">
-        <v>6848290</v>
+        <v>6848168</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5308,10 +5321,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134291270</v>
+        <v>134271302</v>
       </c>
       <c r="B49" t="n">
-        <v>91987</v>
+        <v>83358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5319,33 +5332,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slåttkölen, Hls</t>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523113</v>
+        <v>523319</v>
       </c>
       <c r="R49" t="n">
-        <v>6848141</v>
+        <v>6847932</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5372,12 +5386,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5386,7 +5400,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5405,54 +5418,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134283544</v>
+        <v>134282695</v>
       </c>
       <c r="B50" t="n">
-        <v>99188</v>
+        <v>83358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522963</v>
+        <v>523137</v>
       </c>
       <c r="R50" t="n">
-        <v>6848312</v>
+        <v>6848198</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,69 +5503,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134284129</v>
+        <v>134270518</v>
       </c>
       <c r="B51" t="n">
-        <v>98059</v>
+        <v>79130</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522848</v>
+        <v>523216</v>
       </c>
       <c r="R51" t="n">
-        <v>6848342</v>
+        <v>6848006</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5585,12 +5580,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5605,66 +5600,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134286773</v>
+        <v>134271244</v>
       </c>
       <c r="B52" t="n">
-        <v>99092</v>
+        <v>79130</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220093</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523142</v>
+        <v>523303</v>
       </c>
       <c r="R52" t="n">
-        <v>6848167</v>
+        <v>6847925</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5691,12 +5677,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5711,22 +5697,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134284856</v>
+        <v>134282799</v>
       </c>
       <c r="B53" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5758,10 +5744,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523064</v>
+        <v>523098</v>
       </c>
       <c r="R53" t="n">
-        <v>6848165</v>
+        <v>6848178</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5820,54 +5806,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134284059</v>
+        <v>134283024</v>
       </c>
       <c r="B54" t="n">
-        <v>99188</v>
+        <v>79130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522849</v>
+        <v>523056</v>
       </c>
       <c r="R54" t="n">
-        <v>6848367</v>
+        <v>6848228</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5926,54 +5903,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134285146</v>
+        <v>134283461</v>
       </c>
       <c r="B55" t="n">
-        <v>99188</v>
+        <v>79130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523055</v>
+        <v>523077</v>
       </c>
       <c r="R55" t="n">
-        <v>6848075</v>
+        <v>6848084</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6020,22 +5988,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134283528</v>
+        <v>134283503</v>
       </c>
       <c r="B56" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6067,10 +6035,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522968</v>
+        <v>523084</v>
       </c>
       <c r="R56" t="n">
-        <v>6848309</v>
+        <v>6848078</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6117,22 +6085,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134283275</v>
+        <v>134283801</v>
       </c>
       <c r="B57" t="n">
-        <v>97428</v>
+        <v>79130</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6140,21 +6108,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6164,10 +6132,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523047</v>
+        <v>523140</v>
       </c>
       <c r="R57" t="n">
-        <v>6848112</v>
+        <v>6848077</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6226,10 +6194,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134286052</v>
+        <v>134284856</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6237,21 +6205,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6261,10 +6229,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522811</v>
+        <v>523064</v>
       </c>
       <c r="R58" t="n">
-        <v>6848265</v>
+        <v>6848165</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6323,32 +6291,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134283888</v>
+        <v>134269878</v>
       </c>
       <c r="B59" t="n">
-        <v>99210</v>
+        <v>80488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6358,13 +6326,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522897</v>
+        <v>523151</v>
       </c>
       <c r="R59" t="n">
-        <v>6848375</v>
+        <v>6848140</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6388,12 +6356,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6408,22 +6376,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134285322</v>
+        <v>134270025</v>
       </c>
       <c r="B60" t="n">
-        <v>97428</v>
+        <v>80488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6431,21 +6399,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6423,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523200</v>
+        <v>523174</v>
       </c>
       <c r="R60" t="n">
-        <v>6847770</v>
+        <v>6847988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6485,12 +6453,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6517,10 +6485,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134283498</v>
+        <v>134270228</v>
       </c>
       <c r="B61" t="n">
-        <v>79398</v>
+        <v>80488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6528,21 +6496,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6552,13 +6520,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522978</v>
+        <v>523174</v>
       </c>
       <c r="R61" t="n">
-        <v>6848305</v>
+        <v>6847948</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6582,12 +6550,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6602,44 +6570,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134283986</v>
+        <v>134270952</v>
       </c>
       <c r="B62" t="n">
-        <v>99210</v>
+        <v>80488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6649,10 +6617,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523116</v>
+        <v>523244</v>
       </c>
       <c r="R62" t="n">
-        <v>6848146</v>
+        <v>6847898</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6679,12 +6647,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6711,10 +6679,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134284003</v>
+        <v>134271174</v>
       </c>
       <c r="B63" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6722,21 +6690,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6746,10 +6714,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523115</v>
+        <v>523296</v>
       </c>
       <c r="R63" t="n">
-        <v>6848146</v>
+        <v>6847910</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6776,12 +6744,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6808,10 +6776,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134285939</v>
+        <v>134285727</v>
       </c>
       <c r="B64" t="n">
-        <v>79123</v>
+        <v>80488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6819,21 +6787,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6843,13 +6811,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522853</v>
+        <v>523095</v>
       </c>
       <c r="R64" t="n">
-        <v>6848230</v>
+        <v>6847908</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6893,22 +6861,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134282861</v>
+        <v>134270255</v>
       </c>
       <c r="B65" t="n">
-        <v>5181</v>
+        <v>80493</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6916,21 +6884,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6940,10 +6908,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523134</v>
+        <v>523172</v>
       </c>
       <c r="R65" t="n">
-        <v>6848170</v>
+        <v>6847947</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6970,17 +6938,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7007,32 +6970,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134282799</v>
+        <v>134270268</v>
       </c>
       <c r="B66" t="n">
-        <v>79123</v>
+        <v>80499</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7042,13 +7005,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523098</v>
+        <v>523172</v>
       </c>
       <c r="R66" t="n">
-        <v>6848178</v>
+        <v>6847947</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7072,12 +7035,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7092,44 +7055,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134284567</v>
+        <v>134286811</v>
       </c>
       <c r="B67" t="n">
-        <v>92020</v>
+        <v>57162</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7139,10 +7102,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523213</v>
+        <v>523168</v>
       </c>
       <c r="R67" t="n">
-        <v>6848025</v>
+        <v>6848179</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7175,6 +7138,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7201,57 +7169,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134285196</v>
+        <v>134282861</v>
       </c>
       <c r="B68" t="n">
-        <v>99188</v>
+        <v>5181</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523046</v>
+        <v>523134</v>
       </c>
       <c r="R68" t="n">
-        <v>6848083</v>
+        <v>6848170</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7281,6 +7240,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7295,44 +7259,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134283461</v>
+        <v>134271409</v>
       </c>
       <c r="B69" t="n">
-        <v>79123</v>
+        <v>5201</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>105930</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7342,10 +7306,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523077</v>
+        <v>523339</v>
       </c>
       <c r="R69" t="n">
-        <v>6848084</v>
+        <v>6847893</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7372,12 +7336,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7404,10 +7373,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134283788</v>
+        <v>134282608</v>
       </c>
       <c r="B70" t="n">
-        <v>99210</v>
+        <v>5201</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7415,21 +7384,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>105930</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7439,13 +7408,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>522911</v>
+        <v>523163</v>
       </c>
       <c r="R70" t="n">
-        <v>6848359</v>
+        <v>6848229</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7475,6 +7444,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7489,44 +7463,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134283046</v>
+        <v>134282982</v>
       </c>
       <c r="B71" t="n">
-        <v>79124</v>
+        <v>56925</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>208260</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7536,10 +7510,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523038</v>
+        <v>523056</v>
       </c>
       <c r="R71" t="n">
-        <v>6848219</v>
+        <v>6848227</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7598,32 +7572,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134282695</v>
+        <v>134282904</v>
       </c>
       <c r="B72" t="n">
-        <v>83351</v>
+        <v>99112</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7633,10 +7607,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523137</v>
+        <v>523134</v>
       </c>
       <c r="R72" t="n">
-        <v>6848198</v>
+        <v>6848161</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7695,10 +7669,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134282982</v>
+        <v>134282815</v>
       </c>
       <c r="B73" t="n">
-        <v>56925</v>
+        <v>98219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7706,21 +7680,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>208260</v>
+        <v>219815</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7730,10 +7704,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523056</v>
+        <v>523137</v>
       </c>
       <c r="R73" t="n">
-        <v>6848227</v>
+        <v>6848162</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7780,22 +7754,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134283973</v>
+        <v>134271337</v>
       </c>
       <c r="B74" t="n">
-        <v>99210</v>
+        <v>99099</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7803,21 +7777,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7827,13 +7801,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522850</v>
+        <v>523353</v>
       </c>
       <c r="R74" t="n">
-        <v>6848362</v>
+        <v>6847888</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7857,12 +7831,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7877,44 +7851,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134283939</v>
+        <v>134282795</v>
       </c>
       <c r="B75" t="n">
-        <v>79366</v>
+        <v>99099</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7924,10 +7898,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523131</v>
+        <v>523156</v>
       </c>
       <c r="R75" t="n">
-        <v>6848127</v>
+        <v>6848154</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7986,45 +7960,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134283380</v>
+        <v>134286773</v>
       </c>
       <c r="B76" t="n">
-        <v>79366</v>
+        <v>99099</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523047</v>
+        <v>523142</v>
       </c>
       <c r="R76" t="n">
-        <v>6848103</v>
+        <v>6848167</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8071,57 +8054,61 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134283974</v>
+        <v>134269855</v>
       </c>
       <c r="B77" t="n">
-        <v>99210</v>
+        <v>99195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Slåttkölen, Slåttkölen, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523115</v>
+        <v>523144</v>
       </c>
       <c r="R77" t="n">
-        <v>6848146</v>
+        <v>6848138</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8148,12 +8135,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8180,32 +8167,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134283632</v>
+        <v>134269892</v>
       </c>
       <c r="B78" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8215,10 +8202,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523131</v>
+        <v>523150</v>
       </c>
       <c r="R78" t="n">
-        <v>6848022</v>
+        <v>6848138</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8245,12 +8232,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8274,6 +8261,1290 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134270204</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>523181</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6847951</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134270911</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>523255</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6847886</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>100-tals plantor</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134285146</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>523055</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6848075</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>134285196</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>523046</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6848083</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>134271156</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>523295</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6847909</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134271345</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>523353</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6847889</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134282640</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>523163</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6848219</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134283974</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>523115</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6848146</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134283986</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>523116</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6848146</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134282568</v>
+      </c>
+      <c r="B88" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>523164</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6848212</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134270701</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>523252</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6847973</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>134282793</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>523097</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6848178</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>134285809</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Slåttkölen, Slåttkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>523083</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6847907</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30589-2025 artfynd.xlsx
+++ b/artfynd/A 30589-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283275</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285322</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283498</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283595</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284055</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284727</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270413</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284567</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270019</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270244</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270669</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270739</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270921</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271026</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271170</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271257</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283380</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283632</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283898</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283939</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284003</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284462</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284573</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284836</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285793</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285959</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271302</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282695</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270518</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271244</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282799</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283024</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283461</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283503</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283528</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283801</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284856</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285939</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285967</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283514</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269878</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270228</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270952</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271174</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285727</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270255</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270268</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5430,6 +5675,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134286811</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5532,6 +5782,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282861</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5634,6 +5889,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283696</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5736,6 +5996,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271409</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5838,6 +6103,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282608</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5935,6 +6205,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282982</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6032,6 +6307,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282904</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6129,6 +6409,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282815</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6240,6 +6525,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283829</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6351,6 +6641,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283945</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6457,6 +6752,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284010</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6554,6 +6854,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271337</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6651,6 +6956,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282795</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6757,6 +7067,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134286773</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6858,6 +7173,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269855</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6955,6 +7275,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269892</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7052,6 +7377,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270204</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7154,6 +7484,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270911</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7260,6 +7595,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283544</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7366,6 +7706,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284059</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7472,6 +7817,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285146</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7578,6 +7928,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285196</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7684,6 +8039,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284129</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7781,6 +8141,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271156</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7878,6 +8243,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134271345</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7975,6 +8345,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282640</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8081,6 +8456,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283359</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8187,6 +8567,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283717</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8284,6 +8669,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283743</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8381,6 +8771,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283788</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8478,6 +8873,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283888</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8575,6 +8975,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283961</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8672,6 +9077,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283973</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8769,6 +9179,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283974</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8866,6 +9281,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283986</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8963,6 +9383,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134284143</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9060,6 +9485,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282568</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9157,6 +9587,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270701</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9254,6 +9689,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282793</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9351,6 +9791,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134283046</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9448,6 +9893,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285809</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9545,8 +9995,105 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134286052</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>